--- a/docs/downloads/04/tbl_other_write_sex_marovoay_tous.xlsx
+++ b/docs/downloads/04/tbl_other_write_sex_marovoay_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -407,7 +407,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -430,7 +430,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -476,7 +476,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -499,7 +499,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -522,7 +522,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -545,7 +545,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -568,7 +568,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -591,7 +591,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -683,7 +683,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -706,7 +706,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -752,7 +752,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -775,7 +775,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -798,7 +798,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -890,7 +890,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -936,7 +936,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
